--- a/data/availability/projects/hyde-park-developments/garden-lakes.xlsx
+++ b/data/availability/projects/hyde-park-developments/garden-lakes.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory export for garden-lakes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1209,7 +1219,6 @@
       <c r="G2" t="n">
         <v>73.5</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1220,7 +1229,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1266,7 +1275,6 @@
       <c r="G3" t="n">
         <v>154.0371745</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1277,7 +1285,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1323,7 +1331,6 @@
       <c r="G4" t="n">
         <v>154.0371745</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1334,7 +1341,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1380,7 +1387,6 @@
       <c r="G5" t="n">
         <v>71</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1391,7 +1397,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1437,7 +1443,6 @@
       <c r="G6" t="n">
         <v>106</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1448,7 +1453,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1494,7 +1499,6 @@
       <c r="G7" t="n">
         <v>142</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1505,7 +1509,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1551,7 +1555,6 @@
       <c r="G8" t="n">
         <v>154.0371745</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1562,7 +1565,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1608,7 +1611,6 @@
       <c r="G9" t="n">
         <v>154.0371745</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1619,7 +1621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1665,7 +1667,6 @@
       <c r="G10" t="n">
         <v>68</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1676,7 +1677,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1722,7 +1723,6 @@
       <c r="G11" t="n">
         <v>110</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1779,7 +1779,6 @@
       <c r="G12" t="n">
         <v>105</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1790,7 +1789,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1836,7 +1835,6 @@
       <c r="G13" t="n">
         <v>69</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1847,7 +1845,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1893,7 +1891,6 @@
       <c r="G14" t="n">
         <v>71</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1904,7 +1901,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1950,7 +1947,6 @@
       <c r="G15" t="n">
         <v>154.0371745</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1961,7 +1957,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2007,7 +2003,6 @@
       <c r="G16" t="n">
         <v>154.0371745</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2018,7 +2013,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2064,7 +2059,6 @@
       <c r="G17" t="n">
         <v>68</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2075,7 +2069,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2136,7 +2130,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2182,7 +2176,6 @@
       <c r="G19" t="n">
         <v>106</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2193,7 +2186,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2239,7 +2232,6 @@
       <c r="G20" t="n">
         <v>145</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2250,7 +2242,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2296,7 +2288,6 @@
       <c r="G21" t="n">
         <v>145</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2307,7 +2298,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2353,7 +2344,6 @@
       <c r="G22" t="n">
         <v>105</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2364,7 +2354,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2410,7 +2400,6 @@
       <c r="G23" t="n">
         <v>145</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2421,7 +2410,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2467,7 +2456,6 @@
       <c r="G24" t="n">
         <v>145</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2478,7 +2466,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2539,7 +2527,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2585,7 +2573,6 @@
       <c r="G26" t="n">
         <v>113</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2596,7 +2583,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2642,7 +2629,6 @@
       <c r="G27" t="n">
         <v>117</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2653,7 +2639,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2699,7 +2685,6 @@
       <c r="G28" t="n">
         <v>113</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2710,7 +2695,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2756,7 +2741,6 @@
       <c r="G29" t="n">
         <v>117</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2767,7 +2751,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2813,7 +2797,6 @@
       <c r="G30" t="n">
         <v>152</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2824,7 +2807,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2870,7 +2853,6 @@
       <c r="G31" t="n">
         <v>140.8129819</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2881,7 +2863,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2927,7 +2909,6 @@
       <c r="G32" t="n">
         <v>113</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2938,7 +2919,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2984,7 +2965,6 @@
       <c r="G33" t="n">
         <v>152</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2995,7 +2975,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3041,7 +3021,6 @@
       <c r="G34" t="n">
         <v>152</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3052,7 +3031,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3098,7 +3077,6 @@
       <c r="G35" t="n">
         <v>117</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3109,7 +3087,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3155,7 +3133,6 @@
       <c r="G36" t="n">
         <v>152</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3166,7 +3143,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3212,7 +3189,6 @@
       <c r="G37" t="n">
         <v>150.3636992</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3223,7 +3199,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3269,7 +3245,6 @@
       <c r="G38" t="n">
         <v>150.3636992</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3280,7 +3255,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3326,7 +3301,6 @@
       <c r="G39" t="n">
         <v>150.3636992</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3337,7 +3311,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3383,7 +3357,6 @@
       <c r="G40" t="n">
         <v>150.3636992</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3394,7 +3367,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3455,7 +3428,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3516,7 +3489,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3577,7 +3550,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3638,7 +3611,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3699,7 +3672,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
